--- a/output/2026-09-06_10_Slovenia_Posavska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_10_Slovenia_Posavska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Centro tecnico-commerciale: utensili elettrici e pneumatici, bulloneria/viteria, tecnica di saldatura, noleggio macchine/attrezzature. Assortimento ampio, non specializzato puro. Email non reperita.</t>
+          <t>Centro tecnico-commerciale: utensili elettrici e pneumatici, bulloneria/viteria, tecnica di saldatura, noleggio macchine/attrezzature. Assortimento ampio, non specializzato puro. Email non reperita. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
